--- a/Verificacion_citas_Cap_IV.xlsx
+++ b/Verificacion_citas_Cap_IV.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -638,7 +638,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>(1) SUP-JIN-194/2025: el proyecto de Rodríguez Mondragón reproducido en su voto y las pp. 43-252 del voto están en el tramo del PDF «compressed-1-300» (7.7 MB), cuya descarga agota la sesión de Drive; las notas que remiten a ese tramo quedan pendientes. (2) Ferrer, Prueba sin convicción: el tramo impreso pp. 139-148 no está paginado en las copias descargables; las notas de ese tramo se localizaron por contenido (±1 página).</t>
+          <t>Ferrer, Prueba sin convicción: el tramo impreso pp. 139-148 no está paginado en las copias descargables; las notas de ese tramo se localizaron por contenido (±1 página). El SUP-JIN-194/2025 (voto y proyecto) se cotejó con el PDF en tramos.</t>
         </is>
       </c>
     </row>
@@ -3296,17 +3296,17 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto: tramo del PDF «compressed-1-300» (7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 91, p. 90.</t>
         </is>
       </c>
       <c r="J57" s="7" t="n"/>
@@ -4446,17 +4446,17 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto: tramo del PDF «compressed-1-300» (7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF subido; paginación impresa de cada hoja), párr. 99, p. 93.</t>
         </is>
       </c>
       <c r="J82" s="7" t="n"/>
@@ -4722,17 +4722,17 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto: tramo del PDF «compressed-1-300» (7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF del Drive, tramo 200-300), párr. 493, pp. 243-244: certeza, reglas claras, estables y conocidas; transparencia y verificabilidad.</t>
         </is>
       </c>
       <c r="J88" s="7" t="n"/>
@@ -4768,17 +4768,17 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto, párr. 478, p. 239: tramo del PDF no descargable.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF del Drive, tramo 200-300), párr. 478, p. 239: SUP-CDC-2/2013; renovación periódica; certeza y definitividad.</t>
         </is>
       </c>
       <c r="J89" s="7" t="n"/>
@@ -4998,17 +4998,17 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (tramo no descargable del PDF «compressed-1-300»)</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+          <t>Proyecto de R. Rodríguez Mondragón reproducido en su voto (PDF por tramos 40-120, 121-200 y 200-300)</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto: tramo del PDF «compressed-1-300» (7.7 MB) que no pudo descargarse del Drive.</t>
+          <t>Proyecto de Rodríguez Mondragón reproducido en su voto (PDF del Drive, tramo 200-300), párrs. 481-482 y nota 146, p. 241: art. 41 CPEUM y art. 23.1 CADH (Yatama; Castañeda Gutman).</t>
         </is>
       </c>
       <c r="J94" s="7" t="n"/>
@@ -5231,14 +5231,14 @@
           <t>Voto de R. Rodríguez Mondragón (texto extraído por Drive)</t>
         </is>
       </c>
-      <c r="H99" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Voto de Rodríguez Mondragón, pp. 50-51: fuera del tramo disponible (el texto extraído llega a la p. 42).</t>
+          <t>Voto de Rodríguez Mondragón (PDF subido), pp. 50-51: «priorizar una estabilidad institucional artificial sobre la integridad democrática».</t>
         </is>
       </c>
       <c r="J99" s="7" t="n"/>
@@ -5581,7 +5581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5640,156 +5640,6 @@
       <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Nota: «párrafo tercero» → «párrafo cuarto».</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="n">
-        <v>611</v>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de sentencia presentado por el magistrado Reyes Rodríguez Mondragón en el SUP-JIN-194/2025 y acumulados, reproducido en su voto particular, párrafo 91, p. 90 del voto.</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto: tramo del PDF «compressed-1-300» (7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="n">
-        <v>636</v>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafo 99, p. 93 del voto.</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto: tramo del PDF «compressed-1-300» (7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="n">
-        <v>642</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de sentencia presentado por el magistrado Reyes Rodríguez Mondragón en el SUP-JIN-194/2025 y acumulados, reproducido en su voto particular, párrafo 493, pp. 243 y 244 del voto.</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto: tramo del PDF «compressed-1-300» (7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="n">
-        <v>643</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Ibidem, párrafo 478, p. 239 del voto.</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto, párr. 478, p. 239: tramo del PDF no descargable.</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n">
-        <v>648</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón, cit., párrafos 481 y 482 y nota 146, p. 241 del voto.</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Proyecto de Rodríguez Mondragón reproducido en su voto: tramo del PDF «compressed-1-300» (7.7 MB) que no pudo descargarse del Drive.</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n">
-        <v>653</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Pendiente (fuente no disponible)</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Voto particular del magistrado Reyes Rodríguez Mondragón en el SUP-JIN-194/2025 y acumulados, pp. 50 y 51 del voto.</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Voto de Rodríguez Mondragón, pp. 50-51: fuera del tramo disponible (el texto extraído llega a la p. 42).</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Ninguna; requiere la fuente</t>
         </is>
       </c>
     </row>
@@ -6121,7 +5971,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Conforme (las fuentes normativas se verificaron en las notas).</t>
+          <t>Conforme.</t>
         </is>
       </c>
     </row>
